--- a/data/hospitals/上海市第九人民医院_眼科_医生详细信息.xlsx
+++ b/data/hospitals/上海市第九人民医院_眼科_医生详细信息.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="眼科医生" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="眼科医生信息" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,2038 +425,3767 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="80" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>姓名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>医院</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>科室</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>职称</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>专业方向</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>专业擅长</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>个人简介</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>社会任职</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>获奖荣誉</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>科研成果</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>治疗经验</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>疗效满意度</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>态度满意度</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>病友推荐度</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>doctor_id</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>介绍页URL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>范先群</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>主任医师 教授 院士</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>眼整形眼眶病</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>上睑下垂矫正、活动义眼座植入、眼窝狭窄成形、内眦畸形复位、泪道阻塞再通和眼表修复重建等整形手术；尤其专注于眼眶骨折修复、眼球内陷复位、眼眶畸形矫正和眼眶肿瘤摘除等眼眶手术，先天性小眼球与无眼球整复以及双重睑和眼袋等美容手术</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>范先群，男，主任医师、教授，中国工程院院士。中共党员，医学博士、博士生导师，长江学者特聘教授，上海市重点学科学科带头人，上海交通大学医学院眼科视觉科学研究所所长。主攻眼部肿瘤和眼眶外科，在基础研究和临床治疗方面取得突出成就。</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>第五届亚太地区眼整形外科学会主席；中国眼科内镜专家委员会副主席；中华眼科学会常务委员；中华医学会眼科分会眼整形眼眶病学组组长；上海市医学会眼科专业委员会候任主任委员；上海市科技启明星联谊会理事；国家科技进步奖和国家自然科学基金评审委员；《中华眼视光学与视觉科学》副总编辑；《中华眼科杂志》杂志编委；《Ophthalmology》审稿人</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>上海市优秀青年教师；上海市卫生系统"银蛇奖"；上海市育才奖；上海市医务职工科技创新能手；上海市高尚医德奖；全国卫生系统先进工作者；入选上海市科技"启明星"，上海市卫生系统"百人计划"、上海市优秀学科带头人和上海市领军人才；享受国务院政府特殊津贴；获中华医学奖、教育部和上海市科技进步奖等7项奖项</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>作为第一作者和通讯作者，先后在国内外眼科杂志发表学术论文110余篇（SCI收录21篇），主编和参编专著25本。主持"国家自然科学基金"和上海市重点科研项目20多项。培养博士后、博士和硕士研究生40多名。</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>12876</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/12876/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>傅瑶</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>主任医师 副教授</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>眼表疾病、角膜病、眼整形、白内障</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>眼表疾病、角膜病、眼整形和白内障</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>傅瑶，女，主任医师，博士，博士生导师，眼科主任。2002年毕业于上海第二医科大学获硕士学位并从事眼科临床工作，2007年获上海交通大学医学院眼科学博士学位，2010在美国迈阿密眼表中心作为访问学者一年。擅长诊治各种眼表疾病和角膜病，包括干眼症、翼状胬肉、结膜松弛、眼表外伤、化学伤、睑球粘连和Stevens-Johnson综合症等，以及各种角膜炎、角膜变性和营养不良、角膜先天异常；擅长结膜移植、羊膜移植、口唇粘膜移植、自体和异体角膜缘干细胞移植等多种眼表重建手术和板层角膜移植、穿透性角膜移植手术。同时擅长白内障的诊治和超声乳化手术；眼部整形和美容手术，包括重睑、眼袋、上睑下垂、眼睑畸形整复、义眼座植入、眼窝再造、泪道重建等。</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>中华医学会眼科学分会委员；中华医学会眼科学分会角膜病学组委员；上海眼科学会委员兼秘书</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>教育部高等学校科学技术奖科技进步奖二等奖；中华医学奖三等奖；上海市科技进步二等奖；上海医学科技三等奖</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>发表论文20余篇，其中SCI收录6篇；第一负责人在研和完成国家自然科学基金2项；在研和完成上海市科委基础重点项目等多项。</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>121702676</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/121702676/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>宋欣</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>主任医师</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>眼眶及肿瘤</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>擅长眼肿瘤眼眶病的综合诊疗。尤其是：一、眼肿瘤：1.眼睑肿瘤（皮脂腺癌、鳞状细胞癌、基底细胞癌、黑色素瘤、默克细胞癌、汗腺癌等）2.眼眶肿瘤（泪腺肿瘤、孤立性纤维瘤、神经鞘瘤、脑膜瘤、淋巴瘤、神经纤维瘤、横纹肌肉瘤等）3.结膜肿瘤（黑色素瘤、淋巴瘤、鳞癌等）；二、眼眶病：1.炎性假瘤 2.血管畸形：海绵状血管瘤、静脉畸形、脉管畸形等 3.结节病、木村病、组织细胞增生症、IgG4相关性眼病等</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>宋欣，博士、主任医师，中国抗癌协会眼肿瘤指南认证专家。师承中国工程院院士范先群教授。专业方向为眼肿瘤、眼眶病。尤其擅长眼睑肿瘤和眼眶肿瘤的诊治。所在学科为国家临床重点专科、上海市重点学科和上海市"重中之重"医学重点学科。于世界顶级眼科医院——美国Bascom Palmer眼科中心和英国Moorfields眼科医院长期深造。</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>中国抗癌协会眼肿瘤专委会委员；上海市医学会眼科学分会眼眶病眼整形学组委员；上海医师协会眼科分会</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>2018年国家科技进步二等奖《眼睑和眼眶恶性肿瘤关键诊疗技术体系的建立和应用》；2017年上海市科技进步一等奖《眼内恶性肿瘤关键诊疗技术的建立和应用》；2013年上海市科技进步一等奖《眼肿瘤基因靶向治疗与临床治疗》；获"上海优秀青年医师"、上海交通大学"晨星青年学者"、医院"优秀青年骨干"等称号</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>在国际期刊发表SCI论文二十余篇。负责眼肿瘤方向国家自然科学基金1项及上海市教委等其他市局级课题。参编眼肿瘤学专著及指南撰写，包括《临床眼科肿瘤学》、《整合肿瘤学》、《中国抗癌协会—泪腺腺样囊性癌指南》、《中国抗癌协会—皮脂腺癌指南》、《感官系统复杂病》等。</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>1182080600</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/1182080600/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>周传棣</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>副主任医师</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>玻璃体视网膜疾病</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>专业方向为玻璃体视网膜疾病，擅长眼底病诊疗，包括糖尿病视网膜病变、黄斑水肿、眼底出血、视网膜脱离、黄斑变性、黄斑裂孔、黄斑前膜、视网膜静脉阻塞、高度近视眼底病变、葡萄膜炎、白内障等疑难眼病的手术、激光、药物治疗。</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>周传棣，眼科博士，毕业于上海交通大学医学院，目前任上海第九人民医院副主任医师。目前以第一作者或通讯作者在J Clin Invest（IF:15.9）、Ophthalmology（2篇，IF:13.7）、Prog Retin Eye Res（IF:17.8）等权威期刊发表SCI论文33篇；先后主持国家自然科学面上项目、青年项目各1项，省部级项目2项；入选2024年度上海市"青年拔尖"人才；2022年度上海市"科技创新行动计划"启明星项目（A类），2021年度上海市"医苑新星"青年医学人才培养资助计划，以第一发明人授权专利3项，获"青年临床医学科学家"、"上海市优秀毕业生"等荣誉。</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>入选2024年度上海市"青年拔尖"人才；2022年度上海市"科技创新行动计划"启明星项目（A类）；2021年度上海市"医苑新星"青年医学人才培养资助计划；获"青年临床医学科学家"、"上海市优秀毕业生"等荣誉</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>以第一作者在Ophthalmology等期刊发表论著29篇，主持国家自然科学基金，入选上海市科技启明星；以第一发明人授权专利3项</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>9032289337</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/9032289337/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>徐瓅</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>主治医师</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>青光眼</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>青光眼、白内障、眼睑手术（双眼皮、眼袋等）</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>医学博士。2011年毕业于香港中文大学，获眼科学博士学位，2008年毕业于复旦大学上海医学院（临床医学七年制），获眼科学硕士学位。2011-2014年于复旦大学附属眼耳鼻喉科医院眼科完成住院医师规范化培训。2014年至今于上海交通大学医学院附属第九人民医院眼科工作，2017年开始担任青光眼专业组主治医师。擅长青光眼手术、激光及药物治疗，同时掌握白内障、胬肉、双眼皮、眼袋等眼科常见手术。</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>上海市眼健康促进中心第一届学术委员会健康科普质控专员；上海市黄浦区"眼健康科普宣讲团"成员</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>2023、2024、2025年度好大夫；复旦大学上海医学院青年学者论坛优秀奖；中国医师协会首届中国眼科循证医学与临床研究大会"优秀青年临床科学家"称号；2023人民好医生眼健康科普大赛东部地区眼健康十佳人气作者；首届新时代科普好医"声"推荐活动医学科普优秀奖（文章类）；"花小康"大讲堂人气医师奖</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>发表论文20余篇，多次大会发言交流，参与国家自然科学基金等各级课题7项</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>5753595125</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/5753595125/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>黄筱琳</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>副主任医师</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>眼整形美容</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>眼整形美容，包括重睑术：埋线、切开，开眼角，眼袋手术：内切、外切，上睑下垂，提眉，眼睑内外翻，眼睑肿物，倒睫，眼部肿瘤等。</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>黄筱琳，眼科学博士、副主任医师。2012-2014年在全美综合排名第二的Cleveland Clinic眼科中心做访问学者。师从中国工程院院士、教育部"长江学者"特聘教授、亚太地区眼整形眼眶病学会主席、上海交通大学医学院院长范先群教授。</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>2012年获"上海市科技进步一等奖和教育部科技进步二等奖"；2016年获"九院优秀青年骨干人才"称号</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>在国际专业学术期刊上发表SCI论文10余篇，其中第一作者5篇。以第一完成人身份主持国家自然科学基金项目1项，参与国家973课题及市局级课题数项。</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>5369163772</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/5369163772/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>王俊芳</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>主治医师</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>眼整形美容</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>眼整形美容，包括双眼皮（park改良法，仿生双眼皮，埋线法，全切法，韩式小切口），眉下切皮或提眉，眼袋（微创内切，外切提升），上睑下垂(先天性，老年退行性等)，倒睫，睑内外翻，内眦赘皮，开内外眼角，眼睑肿物，色素痣等眼部美容整形手术等。</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>上海交通大学医学院附属第九人民医院高年资眼整形医生，从事眼科工作20余年，有丰富的眼整形经验，研究领域为眼表疾病及眼整形，在专业学术期刊杂志发表论文10余篇，所在学科为国家重点临床专科。</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>在专业学术杂志发表论文10余篇。</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2326667894</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/2326667894/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>冯伊怡</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>医师</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>眼整形</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>9032332719</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/9032332719/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>王梓</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>主治医师</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>眼整形美容</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>眼整形美容，包括双眼皮手术（埋线法、切开法、韩式小切口），内眦赘皮矫正术（开眼角），眼袋整形手术（内切法、外切法），眼睑松弛矫正术，上睑下垂矫正术。</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>王梓，博士、主治医师，参加临床工作10余年。师从范先群院士，他是第六届亚太地区眼整形外科学会主席。在临床工作中，受朱惠敏老师的言传身教影响颇深，热爱并且专注于眼部整形、美容。</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>在国际专业学术杂志发表SCI收录论文十余篇，其中第一作者及共同第一作者5篇，通讯作者1篇。</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>4799558715</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/4799558715/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>周一雄</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>副主任医师</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>眼肿瘤、眼眶病、眼整形</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>双重睑、眼袋、上睑下垂、眼睑倒睫、眼睑肿物、眼眶肿瘤、眼眶骨折</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>周一雄，副主任医师，专业方向为眼肿瘤、眼眶病、眼整形。2005年本科毕业，2010年于上海交通大学医学院获博士学位。2008-2009年作为访问学者于美国Bascom Palmer眼科中心（全美排名第一）工作。擅长眼眶淋巴瘤、眼眶炎症、眼睑恶性肿瘤的多学科综合治疗，开展眼肿瘤术后的综合整复。所在学科为国家临床重点建设专科、上海市重点学科和上海市"重中之重"医学重点学科。</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>2013年获得上海市科学技术一等奖和教育部科技进步二等奖；获上海市教委"晨光"计划及"优秀青年教师"</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>在国际专业学术杂志发表SCI收录论文数十篇，主要涉及眼肿瘤治疗和修复，眼整形，眼部疾病交叉学科研究。负责国家自然科学基金1项、参与完成上海市自然基金等其他市局级课题7项。</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>1182106648</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/1182106648/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>邵春益</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>主任医师</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>角膜移植、眼表疾病</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>角膜移植、圆锥角膜、角膜皮样瘤、眼表烧伤、眶面裂、睑球粘连、角膜营养不良等难治性眼表疾病眼表重建；角膜炎、干眼病、眼GVHD等诊治；双眼皮、上睑下垂、眼袋、睑缘色素痣、结膜色素痣、倒睫等整形美容手术。</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>邵春益，上海九院眼科主任医师，硕士研究生导师，上海交通大学医学院博士，师从范先群院士。美国哈佛大学医学院麻省眼耳医院博士后。主攻角膜移植、圆锥角膜、角膜皮样瘤、眼表烧伤、眶面裂、睑球粘连等难治性眼表疾病眼表重建。擅长双眼皮、上睑下垂、眼袋、睑缘色素痣、结膜色素痣等整形美容手术。</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>上海市医学会眼科专科分会青年委员会委员、角膜及眼表疾病学组委员；中国医师协会眼科医师分会眼感染学组青年委员会委员；国际泪膜与眼表学会中国分会委员</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>入选上海市浦江人才计划、上海市医苑新星杰出青年医学人才培养计划、上海交通大学医学院双百人计划；获2018美国视觉与眼科研究协会青年临床科学家研究奖（ARVO/Alcon Early Career Clinician-Scientist Research Award）；上海优秀青年医师</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>以第一作者或通讯作者在Am J Ophthalmol、Invest Ophthalmol Vis Sci等杂志发表SCI收录论文20篇。第一负责人承担国家自然科学基金2项，上海市卫生健康委员会卫生行业研究专项（卓越项目）1项，上海交通大学医学院研究型医师项目1项，授权国家发明专利1项，获上海医学科技奖三等奖（第二完成人），副主编《眼表重建》。</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>1314106860</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/1314106860/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>范佳燕</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>主任医师</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>眼肿瘤、眼整形</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>一、主攻视网膜母细胞瘤综合诊疗：1.保眼治疗 2.眼球摘除，义眼座植入，修复，眶内容剜除，多学科联合手术 3.基因检测遗传咨询；二、眼整形美容：包括眼睑肿物切除合并一期重建、重睑术（埋线、切开、韩式小切口）、内眦赘皮矫正（开眼角）、眼袋整形手术（内切、外切、眶隔释放泪沟填充）、上睑下垂、小睑裂综合征、眼睑松弛、眼睑内外翻、倒睫。</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>范佳燕，女，主任医师，医学博士，博士生导师，美国斯坦福大学医学院博士后。专业方向眼肿瘤眼整形。所在学科为国家临床重点专科、上海市重点学科和上海市"重中之重"医学重点学科。国内导师范先群教授为中国工程院院士，教育部"长江学者"特聘教授、中国抗癌协会眼肿瘤专委会主委，中华医学会眼科学会眼整形眼眶病学组组长。</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>国家优秀青年科学基金入选者；上海市科技启明星；上海市青年拔尖人才；上海市医术奖青年科技创新奖；在眼肿瘤方向研究获得2018年国家科技进步二等奖；2017年上海市科技进步一等奖</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>在国际医学专业学术杂志发表SCI收录论文50余篇，其中第一作者/通讯作者37篇；负责国家自然科学基金3项；负责市局级课题7项；参与中国抗癌协会-眼肿瘤（视网膜母细胞瘤）指南</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>5130761743</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/5130761743/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>贾仁兵</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>主任医师 教授</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>眼肿瘤、眼眶病</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>眼肿瘤、眼眶病；主攻眼内肿瘤保眼治疗、眼睑结膜肿瘤Mohs法手术治疗、眼眶肿瘤微创治疗。</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>贾仁兵，上海交通大学特聘教授、主任医师、博士生导师。专业方向眼肿瘤、眼眶病。主攻眼内肿瘤保眼治疗、眼睑结膜肿瘤Mohs法手术治疗、眼眶肿瘤微创治疗。</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>亚太眼肿瘤眼病理学会副主席；英国眼科杂志编委；中国抗癌协会眼肿瘤专委会主任委员；中国医师协会眼科分会眼肿瘤学组副组长；上海市眼科学会眼整形眼眶病学组组长</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>国家"万人计划"领军人才；中国肿瘤青年科学家；上海市"曙光学者"、科技启明星；国家科技进步二等奖；上海市科技进步一等奖；亚太眼科学会成就奖；上海卫生系统"银蛇奖"；上海市卫生系统先进个人；上海市教卫系统优秀共产党员</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>主持国家自然科学重点项目等国家级项目6项。以通讯或第一（含共同）作者在Lancet Child Adolesc Health、Nature Metabolism、Nat Commun、Cell Discov、Sci Adv、Ophthalmology等国际生物医学领域或眼科专业领域杂志发表SCI论文110篇，其中JCR Q1 88篇，IF＞10 34篇。担任第四版中华眼科学第二卷主编、第十版眼科学国家规划本科教材编委等。</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>239529</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/239529/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>苏蕴</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>主治医师</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>白内障</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>3.8</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>9032199149</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/9032199149/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>许诗琼</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>副主任医师</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>眼眶及肿瘤</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>1.各类眼部肿瘤的综合诊治（包括眼睑肿瘤、结膜肿瘤、眼眶肿瘤）2.眼睑肿瘤，尤其是眼睑皮脂腺癌、基底细胞癌、鳞状细胞癌的精准切除联合同期修复 3.结膜肿瘤，黑色素瘤、结膜鳞癌和淋巴瘤的微创手术 4.眼眶肿瘤，尤其是海绵状血管瘤、泪腺肿瘤、神经鞘瘤的根治性手术 5.各类眼睑缺损和畸形修复 6.眼眶炎症包括木村病、结节病、IgG4相关眼病的眼部个性化治疗 7.眼部美容，包括双重睑、眼袋、眼部除皱、提眉等</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>许诗琼，博士，副主任医师。主攻眼睑肿瘤、结膜肿瘤和眼部血管瘤。尤其是眼睑皮脂腺癌、基底细胞癌和结膜黑色素瘤的综合诊治。擅长各类眼睑缺损修复，眼睑疾病、眼部美容。美国MD Anderson肿瘤中心访问科学家；美国哈佛眼耳医院眼整形外科访问医生。博士毕业于上海交通大学医学院，师从范先群院士。</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>中国抗癌协会眼科分会；上海医师协会眼科分会；美国眼整形协会</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>2017年上海市科学技术进步一等奖；2017年上海市科委扬帆计划；2020年上海市卫健委"医苑新星"</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>发表眼肿瘤相关论文近20篇，包括Ophthalmology、JAMA Ophthalmology、British Journal of Ophthalmology、Cancer Letters等。参编书稿3本，包括《中华眼科学年鉴》、《整合肿瘤学》、《眼肿瘤学》等。主持及参加眼肿瘤方向科研项目（课题）及人才计划5项。</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>2973966329</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/2973966329/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>严晨曦</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>主治医师</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>白内障</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>白内障</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>（页面仅有门诊信息，无详细简介）</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>3.8</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>9032336774</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/9032336774/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>沈勤</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>副主任医师 讲师</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>斜视弱视、眼整形</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>斜视、弱视、双重睑、眼袋、上睑下垂、义眼座植入等眼部整形美容术。</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>沈勤，女，副主任医师，1994年毕业于上海交通大学医学院临床医学系，2001年去天津眼科医院斜视弱视及小儿眼科专业学习交流半年。多年来，不断总结创新，特别是在难治性复杂性斜视，如：垂直旋转斜视的诊断和外科治疗以及甲状腺相关眼病以及眼眶骨折后斜视复视的矫正和手术治疗方面形成明显的优势和特色，在国内居领先地位。在斜视弱视、眼部整形方面积累了丰富的临床经验。</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>中华眼科学会上海医学会斜弱视学组第九届副组长；中华眼科学会上海医学会斜弱视学组第十届副组长；中华眼科学会上海医学会视光学学组委员会委员</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>获教育部科技进步奖二等奖；上海市科技进步二等奖等多项科研奖励</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>在《中华眼科杂志》、《实用眼科杂志》等核心刊物发表10多篇论文；以主要参与人承担国自然课题等2项</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>3.8</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>268383</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/268383/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>张蕾蕾</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>副主任医师 副研究员</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>泪器病、眼肿瘤、眼整形美容</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>擅长眼部肿瘤和眼部整形美容的个性化综合诊疗。成人及小儿泪器病的诊断及治疗，尤其是成人及新生儿泪道阻塞、泪囊炎的微创诊疗，包括泪道内窥镜及鼻内镜下泪道微创手术、泪道置管术、难治性泪道疾病的泪道旁路手术；各种类型的双眼皮、内外眦成形术（开眼角）、眼袋、提眉术等眼部精细美容手术；各种类型上睑下垂矫正、睑内翻倒睫矫正、眼睑肿瘤切除及缺损修复等；鼻内镜下微创视神经管减压术用于治疗外伤性神经病变。</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>医学博士，硕士生导师，硕博连读毕业于上海交通大学医学院，师承中国工程院院士范先群教授，专业方向泪器病、眼肿瘤、眼部整形美容以及眼睑病。</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>中国抗癌协会眼肿瘤专业会；亚太眼整形协会终身会员</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>上海市科技进步一等奖；上海市"医苑新星"青年医学人才项目</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>在国际期刊发表SCI论文二十余篇；主持国家自然科学基金2项以及上海市卫健委等其他市局级课题。</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>3.8</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>5763747527</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/5763747527/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>马波</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>副主任医师</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>白内障、眼整形、近视防控</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>1.白内障及晶体疾病（老年性白内障的微切口手术，老花眼白内障联合矫正，糖尿病性白内障的综合治疗，高度近视并发白内障的屈光矫正）2.眼部整形（双眼皮，开眼角，眼袋，倒睫，上睑下垂），眼睑肿物联合整复（黄色瘤，眼睑色素痣），眼表肿物（结膜囊肿，翼状胬肉）3.青少年近视矫正及防控干预（框架眼镜矫正，低浓度阿托品以及角膜塑形镜干预治疗近视，屈光档案筛查随访）</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>医学博士，眼科副主任医师，美国约翰.霍普金斯大学眼科访问学者。擅长各类屈光性白内障手术、眼睑整形美容手术及青少年近视矫正防控等。上海第九人民医院第六届优青骨干，第二轮第四批援滇医疗队专家。在国内外杂志发表论文20余篇，主持承担国家自然科学基金委课题，持有国家实用新型发明专利。</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>上海第九人民医院第六届优青骨干</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>在国内外杂志发表论文20余篇，主持承担国家自然科学基金委课题，持有国家实用新型发明专利。</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>3.8</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>1149383350</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/1149383350/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>胡海林</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>主治医师</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>眼整形美容、泪器疾病</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>眼整形美容手术：个性化设计双重睑（小切口，改良park法，埋线），眼袋（内切、外切），上睑下垂，睑缘肿物美容修复；掌握泪道系统手术：泪道微创内镜手术，严重眼外伤后合并眼睑畸形的泪道重建，鼻泪管再通，新生儿泪囊炎综合治疗，泪囊炎手术失败后再微创修复；微美容手术：肉毒素注射美容祛除鱼尾纹、抬头纹、眼睑痉挛。眼窝再造、义眼植入等手术。</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>主治医师，讲师。毕业于上海交通大学医学院，工作约二十年，专业方向为眼整形眼美容、泪器疾病。所在学科为国家临床重点专科、上海市重点学科和上海市"重中之重"医学重点学科。医院服务明星和优秀志愿者。上海市优秀志愿者，云南省优秀志愿者，上海市优秀青年志愿者。第十八批上海青年志愿者赴滇服务接力队队长。</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>上海市优秀志愿者；云南省优秀志愿者；上海市优秀青年志愿者</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>3.8</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>2359032943</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/2359032943/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>范海燕</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>主治医师</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>眼整形</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>眼整形，包括双眼皮，眼袋，内眦赘皮，上睑下垂，倒睫，胬肉，眼睑肿物，眼周肉毒素注射等</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>毕业于上海交通大学医学院，就职于上海交通大学医学院附属第九人民医院，眼科的主治医师、讲师；熟知眼部的专业知识，将近二十年的临床工作经验。常年钻研于眼部整形与注射微美容，包括双眼皮埋线法，经典切开法，parker法以及开眼角术，眼袋整形术等都有深刻研究。</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>3.8</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>2559753981</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/2559753981/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>王业飞</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>主任医师</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>眼肿瘤、眼眶病、眼整形美容</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>眼肿瘤，眼眶病，眼整形美容手术；颅眶沟通及眶尖占位的内镜微创摘除，内镜下视神经管及眶壁减压；神经纤维瘤病的眼眶重建及眼睑畸形手术修复；眼眶静脉畸形的综合序列治疗；眼部显微整形美容手术，包括Park法双重睑、内眦赘皮矫正和眼袋切除联合眶隔释放重置等。</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>王业飞，上海交通大学医学院附属第九人民医院眼科主任医师，现任上海市解剖学会内镜临床解剖分会副主任委员，上海口腔颌面放射专委会委员。主持国家自然科学基金2项，上海交通大学医工交叉面上项目等多项研究。以通讯或第一（含共同）作者发表SCI论文25篇，主攻眼肿瘤的多学科联合诊疗。</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>上海市解剖学会内镜临床解剖分会副主任委员；上海口腔颌面放射专委会委员</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>主持国家自然科学基金2项，上海交通大学医工交叉面上项目等多项研究。以通讯或第一（含共同）作者发表SCI论文25篇。</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
           <t>3.8</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>1176506741</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/1176506741/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>李一敏</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>主治医师</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>眼表疾病、眼肿瘤、泪器疾病</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>专于眼表疾病，眼肿瘤，泪器疾病，眼整形眼眶病，白内障，青光眼，眼外伤等常见及复杂眼病的诊治和研究；丰富的泪道，眼表肿瘤，眼整形眼眶病，眼外伤，白内障等手术经验。</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>毕业于复旦大学上海医学院（临床医学八年制专业），于复旦大学附属眼耳鼻喉科医院眼科取得博士学位，并完成住院医师规范化培训，获复旦大学优秀毕业生称号。现任职于上海交通大学医学院附属第九人民医院，主攻眼表，泪器，眼外伤，眼肿瘤，白内障等疾病。曾于加拿大英属哥伦比亚大学（UBC）神经眼科，台湾慈济大学等进修实习。</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>获复旦大学优秀毕业生称号；曾获美国视觉与研究大会Travel Grant；参与获得上海市科学进步奖，教育部科学技术奖等</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>发表SCI论文数篇，主持并参与各级课题若干。</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>3.8</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>5133193346</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>https://www.haodf.com/doctor/5133193346/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>李瑾</t>
-        </is>
+      <c r="A25" t="n">
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>上海市第九人民医院</t>
+          <t>罗敏</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>主任医师 教授</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>角膜病、眼整形</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>双眼皮、眼袋、上睑下垂、眼睑结膜肿物美容修复、眼眶结膜囊手术、翼状胬肉、睑球粘连、眼热灼伤、眼化学伤、儿童及成人眼睑缺损整形、眶面裂、角膜移植、角膜皮样瘤。</t>
+          <t>眼科（白内障、眼整形美容、屈光手术）</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>李瑾，女，主任医师，教授，医学博士，博士生导师，眼科教研室副主任。上海市医学会眼科专业委员会角膜病学组委员。美国南阿拉巴马大学医学院访问学者。主要开展角膜移植；羊膜移植、翼状胬肉切除角膜缘移植等眼表重建手术；擅长双重睑、眼袋、小睑裂综合征、结膜囊成形和活动义眼座植入等眼部整形手术；擅长儿童眶面裂畸形矫正、儿童及成人上睑下垂矫正术；擅长各类烧伤或外伤后缺损及粘连矫正，以及眼睑肿瘤切除及美容修复等。</t>
+          <t>白内障、眼部整形及美容，准分子激光手术等</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>上海市医学会眼科专业委员会角膜病学组委员</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+          <t>罗敏，女，主任医师，教授，眼科副主任，教研室主任，眼科学硕士、硕士生导师。上海市残疾人康复专家指导组专家，《国际眼科杂志》特邀编委，《中国实用眼科杂志》通讯委员。上海眼科学会白内障与屈光手术学组副组长。1985年毕业于上海医科大学医学系，1991年获上海第二医科大学眼科学硕士学位。擅长复杂性白内障手术和青光眼、白内障联合手术，以及眼整形美容手术。</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>上海市残疾人康复专家指导组专家；上海眼科学会白内障与屈光手术学组副组长；上海市黄浦区医学会眼科学组组长；中华医学会委员</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1998年院优秀青年培养计划；2001年上海市科技进步奖二等奖；2002年上海市三八红旗手；2007年上海市政府实事项目先进个人；2007年高等学校科技进步二等奖</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>在中华眼科杂志等核心期刊上发表专业论文30余篇，SCI 5篇。副主编、参编专著4本。培养硕士研究生10名。</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>总患者9809位</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>暂无统计</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>74797</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://www.haodf.com/doctor/74797/xinxi-jieshao.html</t>
+          <t>12881</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/12881/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>黄蓉</t>
-        </is>
+      <c r="A26" t="n">
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>上海市第九人民医院</t>
+          <t>周慧芳</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>上海市第九人民医院</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>主任医师 教授</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>眼整形、眼眶病、小儿眼病</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>甲状腺相关性眼病、精准微创眼眶减压手术、眼眶骨折修复手术、重睑及内外眦成形、眼袋矫正、眼部年轻化、上睑下垂矫正、眼睑退缩矫正、活动义眼座植入、眼窝狭窄成形、先天性小眼球整复等</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>周慧芳，主任医师，教授，博士生导师，教育部长江学者特聘教授。上海交通大学医学院附属上海儿童医学中心党委书记，上海交通大学医学院附属第九人民医院眼科眼眶病专业负责人。美国约翰霍普金斯医学院威尔默眼科中心访问学者。亚太TOP 100眼科医生。专业方向：眼整形，眼眶病，小儿眼病。</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>亚太眼整形外科学会（APSOPRS）理事；中国医师协会眼科分会常委、总干事；中华医学会眼科学分会眼免疫学组委员；海医会眼科学专业委员会甲状腺相关性眼病学组副组长；中国医师协会眼科医师分会眼整形眼眶病学组委员；中国女医师协会眼科专委会委员</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2020年上海交通大学校长奖；2019年中国最美女医师；2018年上海市三八红旗手；2017年上海市卫生系统第十六届银蛇奖一等奖；2015年国家科技进步二等奖；2015年教育部高等学校科技进步一等奖；2014年上海市科技进步一等奖；2013年上海市医学科技一等奖</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>承担国家自然科学基金等多项课题，发表SCI论文多篇，培养博士研究生多名。</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>总患者4495位</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>274343</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/274343/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>陆琳娜</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>主任医师 副教授</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>玻璃体视网膜疾病、白内障</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>玻璃体视网膜疾病、复杂性白内障、老年性黄斑病变以及糖尿病视网膜病变慢病管理</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>陆琳娜，眼底病组带头人，主任医师，硕士生导师。研究方向为玻璃体视网膜疾病。目前共发表SCI论文二十余篇。主持及参与研究国家级自然科学基金项目3项，主持上海市科学基金1项。</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>中国抗癌协会眼肿瘤专业委员会常务委员；中国研究型医院学会神经眼科专业委员会委员；上海市医学会眼科学分会眼底病学组委员；上海市中医药学会眼科分会委员</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>中国教育部高等学校科学研究优秀成果奖科技进步奖一等奖；上海市科学技术奖一等奖</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>发表SCI论文二十余篇，主持及参与国家级自然科学基金项目3项，主持上海市科学基金1项。</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>总患者135位</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>89594</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/89594/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>肖彩雯</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>主任医师 副教授</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>眼部微整形、泪道疾病、视神经病变</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>眼部微整形（小切口微创重睑和眼袋去除手术）、泪道阻塞性疾病的微创治疗、视神经病变（内镜微创手术治疗）</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>肖彩雯，女，主任医师，副教授，硕士研究生导师，2009年毕业于上海交通大学，获医学博士学位，师从范先群院士。先后在美国斯坦福大学、加州大学Shiley Eye Center和加州大学洛杉矶分校Jules Stein Eye Institute做访问学者。临床主攻：眼部微整形手术、泪道微创手术、视神经损伤后的功能恢复。</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>国家科技部进步二等奖；上海医学科技奖一等奖；教育部科学技术进步二等奖；河北省优秀医学科技奖一等奖（第一完成人）</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>主持国家自然基金、上海市科委等科研项目9项。发表学术论文27篇，其中SCI收录12篇，参编学术专著5本，主编学术著作1部。</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>总患者2408位</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>121701791</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/121701791/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>李睿</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>医师</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>眼科（眼整形）</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>上睑下垂、倒睫、双眼皮手术、小睑裂、内眦赘皮</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>（页面暂无简介）</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>上睑下垂(1218例) 倒睫(72例) 双眼皮手术(36例) 小睑裂(35例) 内眦赘皮(12例)</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>9032240132</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/9032240132/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>郭文毅</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>主任医师</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>青光眼</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>各类青光眼的药物、激光和手术治疗</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>郭文毅，男，主任医师，第九人民医院眼科副主任，医学博士，博士生导师。上海交通大学医学院眼科视觉科学研究所副所长。澳大利亚西澳大学Lions眼科研究所访问学者和美国Johns Hopkins大学医学院访问教授。擅长各类原发性青光眼、继发性青光眼、先天性青光眼及外伤性低眼压的诊治，掌握各种先进治疗技术。</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>上海市医学会眼科学会委员；上海市眼科学会青光眼学组秘书；中国医师协会询证眼科学组委员；中华医学会委员</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>作为课题负责人，已完成国家自然科学基金面上项目、上海市科委医学引导项目课题、国家863计划子课题等项目。</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>总患者1196位</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>14629</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/14629/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>李琳</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>主任医师 副研究员</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>斜视弱视、儿童眼病、眼整形美容</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>斜视、弱视、儿童眼病、遗传性眼病、基因诊断治疗；眼整形美容（重睑术、内眦赘皮矫正、眼袋整形、上睑下垂等）</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>李琳，女，博士，主任医师，副研究员。从事斜弱视和小儿眼科疾病诊治十余年，中华眼科学会小儿眼科与斜视分会委员。2010年博士毕业于中山大学中山眼科中心，曾在美国国立卫生研究院眼科研究所（NIH/NEI）研究和工作5年。擅长难治性复杂性斜视手术治疗，以及眼整形美容。</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>中华眼科学会小儿眼科与斜视分会委员</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>江苏省卫生厅科技进步一等奖；2015年上海市青年东方学者特聘教授；2016年中华医学会优秀学术论文奖；2017年上海交通大学医学院高峰高原计划-研究型医师</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>主持国家自然基金2项，上海市科研项目1项，教育部留学回国基金1项。发表论文13篇，其中SCI文章9篇。</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>总患者581位</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>4193791790</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/4193791790/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>李伦昊</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>主治医师</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>眼整形、眼眶病、泪道疾病</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>眼眶疾病，鼻泪道疾病，眼科常见病（包括双重睑、眼袋、上睑下垂、眼睑倒睫、眼睑肿物）</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>眼科医师，博士。专业方向眼部整形、眼眶病，泪道疾病。毕业于上海交通大学医学院眼科学。</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>总患者1672位</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2596417320</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/2596417320/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>邓远</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>副主任医师</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>眼眶骨折、眼整形</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>眼眶骨折（精准三维定位导航下微创修复）、眶颧颌复合骨折、创伤性眼眶异物；疤痕性睑内外翻、上睑下垂、双眼皮、眼袋等眼整形手术</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>医学博士，毕业于上海交通大学医学院，擅长眼眶骨折的微创手术修复、三维导航下眼眶复合性骨折的精准复位术、眼部整形美容手术。年完成眼眶骨折手术500例，发表眼眶修复相关的SCI论文30余篇，包括美国眼整形外科学会会刊OPRS 3篇。</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>上海市科技进步一等奖；教育部科技进步一等奖</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>获得国家自然科学基金项目、上海市科技英才扬帆计划。发表SCI论文30余篇。</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>总患者3618位</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>4774334806</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/4774334806/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>计菁</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>主任医师 副教授</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>眼整形，眼睑整形，眼部美容</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>眼整形，眼睑整形，眼部美容</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>计菁，女，主任医师，副教授，博士研究生，自2001年上海第二医科大学临床医学本科毕业后进入九院眼科工作，从事眼科临床工作13年，可独立诊治眼科常见病、多发病及疑难病。临床特色与专长：眼整形眼睑美容手术，眼部微美容。在科研工作中，主要从事眼科干细胞的基础研究。目前作为负责人承担国家自然科学青年基金1项，发表论文共17篇（SCI收录5篇），参编专著《眼整形外科学》。</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>院三八红旗手、院优秀共产党员，2014年上海市优秀团干部，九院三十佳</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>发表论文共17篇（SCI收录5篇），参编专著《眼整形外科学》</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>总患者8296位</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>243828</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/243828/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>施沃栋</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>副主任医师 副教授</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>葡萄膜炎、眼底病</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>葡萄膜炎，眼底病，白内障、眼整形手术；对白塞病，小柳原田病，交感性眼炎，眼弓蛔虫病，血管炎，脉络膜视网膜炎等各种葡萄膜炎的诊断和治疗积累了经验。</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>黄蓉，女，眼科副主任医师，副教授。1997年本科毕业于南京医科大学，2003年获南京医科大学硕士学位，2011年日本筑波大学博士研究生毕业。擅长葡萄膜炎，眼底病等诊断治疗。对白内障，青光眼，角膜病等常见病诊治具有丰富经验。擅长眼显微手术及眼整形手术。</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>上海市医学会眼科分会神经眼科及葡萄膜炎学组委员；上海市中西医结合学会眼科专业委员会委员；海峡两岸医药卫生交流协会风湿免疫病学专业委员会眼免疫学组委员</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>近年来主持或参与国自然、日本公益信托三岛济一记念眼科研究国际交流基金、上海市科委等资助的多项课题。发表国内核心期刊及SCI收入论文10余篇。参编《眼科手术操作技术》一书。</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>731499900</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>https://www.haodf.com/doctor/731499900/xinxi-jieshao.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>周激波</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>眼科</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>主任医师 教授</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>屈光手术、近视防治</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>高度近视和近视眼防治，屈光手术（Smile、TPRK、Fs-LASIK、ICL/TICL植入术、晶状体置换、后巩膜加固），白内障</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>周激波，男，医学博士，主任医师，教授，博士研究生导师。上海九院眼科视光中心主任、眼科副主任。主要从事眼屈光手术和白内障防盲的科研和临床工作。在IOVS、Journal Refractive Surgery等国内外专业期刊发表学术论文论著75篇（第1作者和通讯作者50篇）；参编医学院校教材5部；曾获省级卫生新技术引进成果一等奖、厅局级科技成果二等奖各1次；翻译专著2部；获得授权发明专利1项。</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>中华眼科学会视光学组委员；上海眼科学分会视光和屈光手术学组副组长；中国眼科医师协会视光学分会和摄影分委会委员</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>省级卫生新技术引进成果一等奖；厅局级科技成果二等奖</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>发表学术论文论著75篇（第1作者和通讯作者50篇）；参编医学院校教材5部；翻译专著2部；获得授权发明专利1项；获多项科研项目研究基金资助。</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>241512</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>https://www.haodf.com/doctor/241512/xinxi-jieshao.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>苏文如</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>眼科</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>主任医师 教授</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>葡萄膜炎、眼底病</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>各种常见和疑难葡萄膜炎、巩膜炎、黄斑变性、糖尿病视网膜病变、视网膜血管阻塞、视神经病变、视网膜色素变性等眼底病的诊治；甲状腺相关眼病，过敏性结膜炎和炎症性角膜疾病等眼部炎症性疾病；青睫综合征、病毒性角膜炎、病毒性葡萄膜炎，急性视网膜坏死、巨细胞病毒性视网膜炎等眼部病毒感染性疾病。</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>主任医师，教授，博士生导师，国家杰青和国家优青，羊城好医生。目前担任上海交通大学医学院附属第九人民医院眼科行政副主任，上海地区最大眼免疫与葡萄膜炎中心负责人。原中山大学中山眼科中心眼免疫与葡萄膜炎科主任。在中山大学中山眼科中心从事眼科临床、科研、教学工作二十年，擅长各种常见和疑难葡萄膜炎、眼底病的诊治。</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>上海市免疫学会眼免疫分会副主任委员；中国研究型医院学会眼科专委会委员；广东省医师协会眼科学分会眼与全身病组副组长</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>国家杰出青年科学基金获得者；国家优秀青年科学基金获得者；羊城好医生；广东省科技进步一等奖1项；授权发明专利3项</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>主持国家优秀青年基金，国家重点研发课题1项，国家自然科学基金2项等13项课题，发表SCI论文130余篇，论文成果被编入教科书。培养研究生32名。</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>4685912282</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>https://www.haodf.com/doctor/4685912282/xinxi-jieshao.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>林明</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>眼科</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>眼眶外科，泪道手术，眼部整形</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>眼眶骨折微创整复，小儿先天性上睑下垂，成人复发性上睑下垂，泪道微创再通，复杂眼外伤整形，眼部美容整形</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>施沃栋，男，副主任医师，副教授，2001年上海第二医科大学本科毕业，2011年上海交通大学医学院博士毕业，2013年晋升副主任医师。主攻专业：眼眶外科，泪道手术，眼部整形。每年完成眼眶骨折修复100例以上，泪道200例以上，眼睑200例以上。手术安全，恢复快。</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>在国内外发表论文10余篇，其中SCI论文3篇发表在国际专业杂志《PLASTIC &amp;RECONSTRUCTIVE SURGERY》《RETINA》及《JOURNAL OF CRANIOFACIAL SURGERY》</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>总患者9129位</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>599835869</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/599835869/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>韩艳平</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>主治医师</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>眼肿瘤 眼整形 眼部疾患 常见眼部疾病的诊治</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>（页面未填写）</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>总患者631位</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>6964485281</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/6964485281/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>朱冬青</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>主任医师 副教授</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>眼底病、白内障</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>视网膜脱离、眼底出血、黄斑变性、白内障、眼外伤等复杂眼病、眼部美容手术</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>朱冬青，男，主任医师，博士，2007年博士毕业于上海交通大学医学院。专业特长为眼底病、白内障。擅长视网膜脱离、糖尿病性视网膜病变、黄斑病变、眼底出血、高度近视脉络膜新生血管生长等复杂眼病的激光及显微手术治疗、白内障超声乳化吸除和人工晶体植入术。在国际上首次报道应用羊膜移植治疗难治性脉络膜缺损；首次报道应用全血覆盖代替气体充填治疗黄斑裂孔。</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>上海市医学科技奖一等奖</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>主持与参与市级自然基金课题一项、国家自然基金课题二项。发表国内外学术论文30余篇，国外SCI收录16篇。</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>总患者1060位</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>162214250</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/162214250/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>韩明磊</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>主任医师</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>眼眶肿瘤、眼整形</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>上睑下垂；眼睑美容手术（双眼皮，眼袋及其修复）；眼睑、眼眶肿瘤的诊断和综合治疗；眼眶爆裂性骨折、复合性眼眶骨折的整复；眼眶血管瘤、血管畸形的诊治；眼部炎性假瘤、淋巴瘤、IgG4相关性眼病的诊治；眼睑、结膜恶性黑色素瘤的综合治疗；眼窝畸形的整复，睑球粘连、结膜囊狭窄及赝复体治疗等。</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>林明，男，主任医师，医学博士。1993年毕业于上海交通大学医学院，2018年获眼科学博士学位，导师范先群教授。2015年晋升主任医师。参加眼科临床工作28年，积累了丰富的临床经验，专长眼眶肿瘤的诊断和治疗，如眼眶血管瘤、血管畸形、炎性假瘤、淋巴瘤、神经纤维瘤等的诊治，擅长复合性眼眶骨折的整复，上睑下垂的手术治疗，先天性眼窝畸形的整复，眼部整形美容，睑球粘连、结膜囊狭窄等。</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>中华医学会眼整形眼眶病学组委员；中国医师协会眼眶病眼整形专委会委员兼秘书；中国抗癌协会眼肿瘤专业委员会委员；亚太眼整形美容协会（APSOPRS）委员；上海医学会眼科分会眼整形眼眶病学组委员；上海抗癌协会黑色素瘤专委会常委</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>上海市科技进步一、二等奖；上海医学科技三等奖；中华医学科技奖三等奖；教育部科技进步二等奖；上海市杰出青年志愿者荣誉称号</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>在国内外期刊先后发表学术论文70余篇，参编眼科专著5本，副主编1本，出版卫生部眼科视听教材2部。目前在研负责国家自然科学基金面上项目1项、上海市重点学科课题1项。</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>12869</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>https://www.haodf.com/doctor/12869/xinxi-jieshao.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>刘星彤</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>眼科</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>儿童眼肿瘤及儿童眼底病变</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>儿童眼肿瘤及儿童眼底病变特别是视网膜母细胞瘤（Rb）、早产儿视网膜病变（ROP）、Coats、FEVR等，成人玻璃体视网膜病变，斜视、弱视、屈光不正、泪道疾病、眼表疾病</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>韩明磊，国际眼肿瘤学会成员，美国眼科学会成员，医学博士，国内师从小儿眼科专家刘桂香教授及王利华教授，2015年-16年作为访问学者赴美国著名的Wills眼科医院眼肿瘤研究所、小儿眼底病科交流访问，师从眼肿瘤专家Carol L.Shields教授，主修视网膜母细胞瘤。发表SCI论文3篇，国内核心期刊6篇，主编眼科学著作5部，专利3项。</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>国际眼肿瘤学会成员；美国眼科学会成员</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>发表SCI论文3篇，国内核心期刊6篇，主编眼科学著作5部，专利3项</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>总患者2237位</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2269769504</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/2269769504/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>李寅炜</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>副主任医师</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>眼眶病</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>甲状腺眼病、甲亢突眼的综合诊疗；眼眶骨折、眼眶外伤的手术治疗；骨纤维异常增殖症、先天性眶面畸形的多学科联合诊疗；眼整形美容：包括双重睑、眼袋、上睑下垂、眼睑倒睫、眼睑肿物等</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>上海交通大学医学院附属第九人民医院眼科副主任医师，眼科学博士。本硕博均毕业于上海交通大学医学院，师从中国工程院院士范先群教授。主攻方向为眼眶病，尤其是甲状腺眼病、骨纤维异常增殖症、先天性眶面畸形、眼眶骨折等复杂眼眶病的综合诊疗。深耕数字化眼眶外科领域，创建具有自主知识产权的内镜导航手术系统，开展眼眶外科手术机器人的相关研究。</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2023年上海市科学技术一等奖；2017年上海市优秀住院医师；2015年国家科学技术进步二等奖；2014年上海市科学技术一等奖；2014年教育部科技进步一等奖；2014年上海医学科技一等奖</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>总患者1348位</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>5489644691</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/5489644691/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>季雍容</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>副主任医师</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>斜弱视、小儿眼病；眼整形、眼外伤、眼眶病</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>斜弱视、小儿眼病：各类斜视弱视、屈光不正、倒睫、上睑下垂、泪道阻塞等；眼整形、眼外伤、眼眶病：眼部整形（双眼皮、眼袋手术等）、眼部肿物切除及美观修复、眼部外伤的后期修复、甲状腺相关眼病（突眼）等眼眶病</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>季雍容，博士（M.D.&amp; Ph.D.），眼科副主任医师，上海交通大学医学院临床医学专业法文班毕业，师从中国工程院院士范先群教授。2015年通过"国际眼科医师临床知识考试"，荣获中国区第一名。曾在法国巴黎Avicenne医院、英国伦敦Royal Free医院、以色列耶路撒冷希伯来大学进修。于国际期刊发表专业论著10余篇，主持国家自然科学基金1项、上海市科委基金1项。</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2015年国际眼科医师临床知识考试中国区第一名</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>于国际期刊发表专业论著10余篇，主持国家自然科学基金1项、上海市科委基金1项</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>总患者297位</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>6964570435</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/6964570435/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>张思奕</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>眼科（角膜科）</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>住院医师</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>角膜科</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>专业方向为眼表角膜病，擅长常见眼科疾病的诊治</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2021年毕业于上海交通大学医学院，现就职于上海交通大学医学院附属第九人民医院眼科</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>总患者29位</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>9032383780</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/9032383780/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>徐晓芳</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>主任医师</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>玻璃体视网膜疾病；眼内恶性肿瘤；眼整形美容</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>玻璃体视网膜疾病的临床诊治，包括复杂性视网膜脱离，糖尿病视网膜病变，黄斑疾病的手术治疗。尤其擅长眼内恶性肿瘤，包括视网膜母细胞瘤和葡萄膜黑色素瘤的保眼治疗。眼整形美容，包括双重睑成形术、眼角开大术、眼袋整形手术、上睑下垂矫正术</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>主任医师，博士，2007年硕士毕业于复旦大学附属眼耳鼻喉科医院，2010年毕业于上海交通大学医学院附属第九人民医院，师从范先群教授（中国工程院院士）。2014-2015年在美国斯坦福大学医学院访学一年。发表SCI论文30余篇，以第一和/或通讯作者发表SCI论文16篇。</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>上海市医学会眼科学分会眼底病学组委员；中国医师协会眼科医师分会儿童眼健康专委会委员</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2012年上海市科技进步一等奖；2013年教育部科技进步二等奖；2017年上海市科技进步一等奖；2018年国家科技进步二等奖</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>发表SCI论文30余篇，以第一和/或通讯作者发表SCI论文16篇；参与完成国家自然科学基金5项</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>总患者1586位</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>599842397</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/599842397/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>郭涛</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>主任医师</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>白内障、青光眼、视网膜脱离、眼外伤</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>白内障、青光眼、视网膜脱离、眼外伤等疾病的诊治，特别是白内障超声乳化术（高度近视，老花合并白内障等白内障屈光手术）、青光眼、视网膜疾病显微手术治疗；高度近视屈光手术等（ICL植入术）</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>郭涛，男，主任医师，九院北院眼科主任，眼科学博士。曾在美国内布拉斯加州大学医学中心做访问学者。擅长白内障、青光眼、视网膜脱离、眼外伤等疾病的诊治，白内障手术量超万例。曾获全国百名优秀志愿者、病人心中最满意的医生、杨浦区"十大杰出青年"等荣誉称号。</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>中华医学会眼科学分会防盲和流行病学组委员；上海市医学会眼科学分会委员；海医会白内障和屈光手术学组委员；上海市医学会眼科学分会白内障学组委员</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>全国百名优秀志愿者；病人心中最满意的医生；杨浦区"十大杰出青年"</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>总患者784位</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>300443</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/300443/xinxi-jieshao.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>李芳</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>上海市第九人民医院</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>主治医师</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>眼整形眼眶病、斜视</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>斜视弱视；重睑、睑袋等眼整形手术及咨询，眼周注射美容；甲状腺眼病诊治，眼睑退缩注射治疗；眼睑肿物、倒睫、上睑下垂诊治，以及结膜炎、干眼症、霰粒肿等眼科常见病诊治。</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>主治医师，医学博士，毕业于上海交通大学医学院，师从范先群教授、周慧芳教授，专业方向眼整形眼眶病、斜视。</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>5552074465</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>https://www.haodf.com/doctor/5552074465/xinxi-jieshao.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>王洋</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>上海市第九人民医院</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>眼科</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>主治医师</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>眼科</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>9032080575</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>https://www.haodf.com/doctor/9032080575/xinxi-jieshao.html</t>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>视光及屈光手术</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>儿童近视防控，成人近视矫正手术（全飞秒、个性化微飞秒、ICL植入术）及白内障手术</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>李芳，博士，主治医师，上海交通大学优秀毕业生，师承范先群院士。入选"希望之星"中国眼科医生菁英计划。临床聚焦视光及屈光手术方向。</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>上海交通大学优秀毕业生；入选"希望之星"中国眼科医生菁英计划</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>（页面未显示）</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>总患者227位</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>暂无统计</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>6964567925</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>https://www.haodf.com/doctor/6964567925/xinxi-jieshao.html</t>
         </is>
       </c>
     </row>
